--- a/data/trans_bre/P45C_R1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Provincia-trans_bre.xlsx
@@ -665,12 +665,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,11</t>
+          <t>-4,31; 0,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,01</t>
+          <t>-4,08; 1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,5; 110,85</t>
+          <t>-100,0; 68,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,54; 137,4</t>
+          <t>-77,62; 114,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,0</t>
+          <t>-2,34; 1,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,01</t>
+          <t>-2,11; -0,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,71</t>
+          <t>-0,44; 1,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,33</t>
+          <t>-1,96; 3,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 98,35</t>
+          <t>-58,92; 106,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 150,55</t>
+          <t>-100,0; 332,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,23; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 125,57</t>
+          <t>-35,19; 126,68</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,02</t>
+          <t>1,14; 5,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,0</t>
+          <t>-1,54; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,64</t>
+          <t>0,05; 1,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,73</t>
+          <t>-4,81; -0,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,82</t>
+          <t>-3,17; 2,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,82</t>
+          <t>-0,24; 3,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -0,05</t>
+          <t>-2,65; 0,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,81</t>
+          <t>-100,0; -16,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,17; 119,0</t>
+          <t>-55,99; 118,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 1156,13</t>
+          <t>-35,14; 891,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,42</t>
+          <t>-100,0; 147,8</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-2,43; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,36</t>
+          <t>-1,39; 1,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,32</t>
+          <t>-1,84; 2,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,19</t>
+          <t>-0,5; 3,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,97</t>
+          <t>-2,13; 2,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 600,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 257,99</t>
+          <t>-66,25; 222,23</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,4</t>
+          <t>-1,43; 2,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,91</t>
+          <t>-0,46; 1,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,57</t>
+          <t>-1,94; 0,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,86</t>
+          <t>-3,12; 0,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 164,39</t>
+          <t>-46,24; 164,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-41,72; 502,15</t>
+          <t>-40,94; 400,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,62; 226,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-78,17; 75,74</t>
+          <t>-78,52; 69,15</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,15</t>
+          <t>-0,69; 2,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,28</t>
+          <t>-0,26; 1,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,1</t>
+          <t>-0,47; 1,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,36</t>
+          <t>-1,59; 0,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 191,95</t>
+          <t>-32,65; 224,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 655,22</t>
+          <t>-74,69; 654,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-92,73; 95,39</t>
+          <t>-88,37; 106,86</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,6</t>
+          <t>-0,67; 0,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,87</t>
+          <t>-0,3; 0,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,71</t>
+          <t>-0,29; 0,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,47</t>
+          <t>-0,94; 0,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 44,34</t>
+          <t>-33,1; 47,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 86,68</t>
+          <t>-21,59; 83,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 100,73</t>
+          <t>-26,87; 106,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 37,47</t>
+          <t>-44,58; 38,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R1-Provincia-trans_bre.xlsx
@@ -665,12 +665,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,61</t>
+          <t>-4,36; 0,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,81</t>
+          <t>-4,06; 1,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,59</t>
+          <t>-100,0; 76,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-77,62; 114,78</t>
+          <t>-77,91; 112,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,97</t>
+          <t>-2,31; 1,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; -0,1</t>
+          <t>-2,14; 0,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,7</t>
+          <t>-0,46; 1,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,54</t>
+          <t>-2,63; 2,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,92; 106,43</t>
+          <t>-58,01; 111,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 332,17</t>
+          <t>-100,0; 242,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-69,6; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 126,68</t>
+          <t>-43,83; 116,65</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,3</t>
+          <t>1,16; 5,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,0</t>
+          <t>-1,65; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,67</t>
+          <t>0,18; 1,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-76,77%</t>
+          <t>-63,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,81; -0,74</t>
+          <t>-4,87; -0,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,78</t>
+          <t>-3,04; 2,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,66</t>
+          <t>-0,11; 3,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,02</t>
+          <t>-2,51; 0,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,94</t>
+          <t>-100,0; -3,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 118,0</t>
+          <t>-53,42; 115,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 891,32</t>
+          <t>-30,83; 1014,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 147,8</t>
+          <t>-100,0; 124,19</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,0</t>
+          <t>-1,85; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,41</t>
+          <t>-1,55; 1,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,52</t>
+          <t>-1,85; 2,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,1</t>
+          <t>-0,77; 3,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,5</t>
+          <t>-2,13; 2,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,67; 790,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,25; 222,23</t>
+          <t>-59,97; 303,87</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,02</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-32,85%</t>
+          <t>-0,78%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,29</t>
+          <t>-1,64; 2,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,91</t>
+          <t>-0,46; 1,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,64</t>
+          <t>-1,77; 0,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,91</t>
+          <t>-1,94; 1,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 164,09</t>
+          <t>-49,93; 155,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,94; 400,38</t>
+          <t>-44,89; 462,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 226,26</t>
+          <t>-87,66; 148,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-78,52; 69,15</t>
+          <t>-60,6; 140,17</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-56,07%</t>
+          <t>-67,66%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,24</t>
+          <t>-0,77; 2,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,27</t>
+          <t>-0,14; 1,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,18</t>
+          <t>-0,47; 1,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,41</t>
+          <t>-2,21; -0,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 224,85</t>
+          <t>-29,83; 218,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,69; 654,56</t>
+          <t>-69,5; 791,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,37; 106,86</t>
+          <t>-92,57; 12,48</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-11,78%</t>
+          <t>-9,87%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,65</t>
+          <t>-0,63; 0,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,88</t>
+          <t>-0,25; 0,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,72</t>
+          <t>-0,29; 0,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,44</t>
+          <t>-0,8; 0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 47,06</t>
+          <t>-31,66; 48,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 83,81</t>
+          <t>-15,74; 84,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 106,1</t>
+          <t>-26,14; 101,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 38,0</t>
+          <t>-38,07; 35,07</t>
         </is>
       </c>
     </row>
